--- a/K리그 2_2026.xlsx
+++ b/K리그 2_2026.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T145"/>
+  <dimension ref="A1:T177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14432,11 +14432,19 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr"/>
-      <c r="I138" s="2" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
           <t>3</t>
@@ -14529,11 +14537,19 @@
           <t>16</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr"/>
-      <c r="I139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -14620,11 +14636,19 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr"/>
-      <c r="I140" s="2" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -14717,8 +14741,16 @@
           <t>4</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr"/>
-      <c r="I141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
           <t>5</t>
@@ -14811,11 +14843,19 @@
           <t>14</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr"/>
-      <c r="I142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -14905,8 +14945,16 @@
           <t>9</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr"/>
-      <c r="I143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
           <t>15</t>
@@ -14999,11 +15047,19 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr"/>
-      <c r="I144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -15090,64 +15146,3272 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>화성FC</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="P145" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q145" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="R145" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="S145" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T145" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>07.24</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>김해FC</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>충북청주</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R146" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="S146" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T146" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>07.24</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>서울E</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>천안시티FC</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="P147" s="2" t="inlineStr">
+        <is>
+          <t>2.5/3</t>
+        </is>
+      </c>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="R147" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S147" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T147" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>07.25</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>수원삼성</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R148" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S148" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T148" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>07.25</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>수원FC</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="P149" s="2" t="inlineStr">
+        <is>
+          <t>3/3.5</t>
+        </is>
+      </c>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="R149" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="S149" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T149" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>07.25</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>화성FC</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>충남아산</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T150" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>07.25</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="P151" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="R151" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="S151" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T151" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>07.26</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>김포</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr"/>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr">
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>용인시민축구단</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="R152" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>0.5/1</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>07.26</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>파주시민</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>안산</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="R153" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="S153" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T153" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>08.01</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>충남아산</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>성남</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="R154" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>08.01</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>천안시티FC</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>용인시민축구단</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="P155" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="R155" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S155" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T155" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>08.01</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>충북청주</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>수원삼성</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="R156" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="S156" s="2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="T156" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>08.01</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>화성FC</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K145" s="2" t="inlineStr">
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="inlineStr">
+        <is>
+          <t>2.5/3</t>
+        </is>
+      </c>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="R157" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="S157" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T157" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>08.02</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>안산</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>김해FC</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R158" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="S158" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>08.02</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>서울E</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="inlineStr">
+        <is>
+          <t>2.5/3</t>
+        </is>
+      </c>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="R159" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="S159" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T159" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>08.02</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>김포</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R160" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S160" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T160" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>08.02</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>파주시민</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R161" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="S161" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T161" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>08.07</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>충남아산</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>안산</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="inlineStr">
+        <is>
+          <t>2.5/3</t>
+        </is>
+      </c>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="R162" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S162" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T162" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>08.07</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>김포</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>충북청주</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="P163" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="R163" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="S163" s="2" t="inlineStr">
+        <is>
+          <t>0.5/1</t>
+        </is>
+      </c>
+      <c r="T163" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>08.07</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="inlineStr">
+        <is>
+          <t>2.5/3</t>
+        </is>
+      </c>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="R164" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>08.07</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>화성FC</t>
         </is>
       </c>
-      <c r="L145" s="2" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="M145" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>서울E</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="R165" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="S165" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T165" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>08.07</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>수원삼성</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>김해FC</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>2.5/3</t>
+        </is>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>08.07</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>용인시민축구단</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="R167" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="S167" s="2" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T167" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>08.08</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>파주시민</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>수원FC</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="inlineStr">
+        <is>
+          <t>2.5/3</t>
+        </is>
+      </c>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R168" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>-0.5/1</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>08.08</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>성남</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>천안시티FC</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="R169" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>08.15</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>부산</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr"/>
+      <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>화성FC</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr">
+        <is>
+          <t>2.5/3</t>
+        </is>
+      </c>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="R170" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>08.15</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>충북청주</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr"/>
+      <c r="I171" s="2" t="inlineStr"/>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>전남</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
         <is>
           <t>3.10</t>
         </is>
       </c>
-      <c r="N145" s="2" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="O145" s="2" t="inlineStr">
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R171" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S171" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T171" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>08.15</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>김해FC</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr"/>
+      <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>경남</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="R172" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>08.15</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>수원삼성</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr"/>
+      <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>수원FC</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="inlineStr">
+        <is>
+          <t>2.5/3</t>
+        </is>
+      </c>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="R173" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="S173" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T173" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>08.16</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>대구</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr"/>
+      <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>충남아산</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="R174" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S174" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T174" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>08.16</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>김포</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr"/>
+      <c r="I175" s="2" t="inlineStr"/>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>천안시티FC</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>1.98</t>
         </is>
       </c>
-      <c r="P145" s="2" t="inlineStr">
+      <c r="P175" s="2" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="Q145" s="2" t="inlineStr">
+      <c r="Q175" s="2" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="R145" s="2" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="S145" s="2" t="inlineStr">
-        <is>
-          <t>0/-0.5</t>
-        </is>
-      </c>
-      <c r="T145" s="2" t="inlineStr">
-        <is>
-          <t>2.05</t>
+      <c r="R175" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S175" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T175" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>08.16</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>파주시민</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr"/>
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>성남</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>K리그 2</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>08.16</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>서울E</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr"/>
+      <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>안산</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
